--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/ALABAMA_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/ALABAMA_2013.xlsx
@@ -3012,7 +3012,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C148">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C239">
@@ -10662,7 +10662,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C573">
@@ -12174,7 +12174,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C657">
@@ -17628,7 +17628,7 @@
       </c>
       <c r="B960" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C960">
@@ -19860,7 +19860,7 @@
       </c>
       <c r="B1084" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1084">
